--- a/doc CONESAAAA/DATOS CORREGIDOS.xlsx
+++ b/doc CONESAAAA/DATOS CORREGIDOS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivan\Documents\gitPrimer-Semestre-25\doc CONESAAAA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96827A3A-86E9-4961-BCFD-C3AEFA9BAC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B549EB95-DF38-41CF-B7F6-A6BCC7AE9EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="0" windowWidth="10245" windowHeight="10920" xr2:uid="{993547E2-7941-42F8-946B-829C64FB54A3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{993547E2-7941-42F8-946B-829C64FB54A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>SI PAVIMENTADO</t>
   </si>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>AVENIDA 5</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
   </si>
 </sst>
 </file>
@@ -114,12 +117,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -143,10 +152,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -465,9 +478,10 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="F2" t="s">
+      <c r="E2" s="4" t="s">
         <v>0</v>
       </c>
+      <c r="F2" s="4"/>
     </row>
     <row r="4" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E4" t="s">
@@ -634,6 +648,9 @@
       </c>
     </row>
     <row r="27" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="E27" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="F27">
         <f>SUM(F4:F25)</f>
         <v>16699.78</v>
@@ -647,6 +664,9 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E2:F2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>